--- a/A2259C_A_MARKER.xlsx
+++ b/A2259C_A_MARKER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myrp-my.sharepoint.com/personal/paul_z_chen_rp_edu_sg/Documents/A2259C/A2295C graded assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="344" documentId="11_79039D3FD5A59840DAA791CC085518F7C3A803AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5BC00BB-25A5-4B35-99BF-8C65934D1D15}"/>
+  <xr:revisionPtr revIDLastSave="355" documentId="11_79039D3FD5A59840DAA791CC085518F7C3A803AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4019CFB-E9B2-482C-A13A-0BF51EB008C7}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Meta" sheetId="8" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="281">
   <si>
     <t>Outlet_ID</t>
   </si>
@@ -949,6 +949,15 @@
 3. biodiverse planting.
 At each site, a biodiversity index score was recorded based on species richness and abundance surveys.
 The study aims to examine whether verge management regime is associated with variation in biodiversity index scores.</t>
+  </si>
+  <si>
+    <t>Briefly discuss one limitation of relying on generative AI to solve this question.</t>
+  </si>
+  <si>
+    <t>AI may suggest an incorrect model if context is misunderstood 
+AI may not correctly handle dummy variable creation in Excel 
+AI may give generic interpretations without checking assumptions 
+AI outputs depend on correct user input and may overlook data issues</t>
   </si>
 </sst>
 </file>
@@ -1049,7 +1058,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1079,6 +1088,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3177,13 +3190,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18DE6AB0-6A48-4A36-9BFC-9A613170FEA3}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>271</v>
       </c>
@@ -3192,7 +3205,7 @@
       </c>
       <c r="C1" s="9"/>
     </row>
-    <row r="2" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>273</v>
       </c>
@@ -3201,7 +3214,7 @@
       </c>
       <c r="C2" s="9"/>
     </row>
-    <row r="3" spans="1:3" ht="225" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="216" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>275</v>
       </c>
@@ -3210,7 +3223,7 @@
       </c>
       <c r="C3" s="9"/>
     </row>
-    <row r="4" spans="1:3" ht="300" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>277</v>
       </c>
@@ -3227,9 +3240,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B70"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3237,7 +3250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3245,7 +3258,7 @@
         <v>15.54</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3253,7 +3266,7 @@
         <v>8.5399999999999991</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -3261,7 +3274,7 @@
         <v>11.14</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -3269,7 +3282,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -3277,7 +3290,7 @@
         <v>9.1199999999999992</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -3285,7 +3298,7 @@
         <v>10.220000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -3293,7 +3306,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -3301,7 +3314,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3309,7 +3322,7 @@
         <v>10.11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -3317,7 +3330,7 @@
         <v>18.07</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -3325,7 +3338,7 @@
         <v>11.17</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -3333,7 +3346,7 @@
         <v>11.87</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -3341,7 +3354,7 @@
         <v>12.26</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -3349,7 +3362,7 @@
         <v>13.94</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -3357,7 +3370,7 @@
         <v>14.98</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -3365,7 +3378,7 @@
         <v>11.57</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -3373,7 +3386,7 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -3381,7 +3394,7 @@
         <v>8.36</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3389,7 +3402,7 @@
         <v>9.1199999999999992</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3397,7 +3410,7 @@
         <v>11.22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -3405,7 +3418,7 @@
         <v>7.99</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -3413,7 +3426,7 @@
         <v>10.26</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -3421,7 +3434,7 @@
         <v>13.35</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -3429,7 +3442,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -3437,7 +3450,7 @@
         <v>9.4499999999999993</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -3445,7 +3458,7 @@
         <v>10.210000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -3453,7 +3466,7 @@
         <v>9.7899999999999991</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -3461,7 +3474,7 @@
         <v>12.93</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -3469,7 +3482,7 @@
         <v>9.7799999999999994</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -3477,7 +3490,7 @@
         <v>11.17</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -3485,7 +3498,7 @@
         <v>10.35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -3493,7 +3506,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -3501,7 +3514,7 @@
         <v>11.15</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -3509,7 +3522,7 @@
         <v>16.329999999999998</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -3517,7 +3530,7 @@
         <v>11.31</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -3525,7 +3538,7 @@
         <v>10.33</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -3533,7 +3546,7 @@
         <v>9.77</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -3541,7 +3554,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -3549,7 +3562,7 @@
         <v>11.02</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -3557,7 +3570,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -3565,7 +3578,7 @@
         <v>13.33</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -3573,7 +3586,7 @@
         <v>8.69</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -3581,7 +3594,7 @@
         <v>10.56</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -3589,7 +3602,7 @@
         <v>11.54</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -3597,7 +3610,7 @@
         <v>14.33</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -3605,7 +3618,7 @@
         <v>12.96</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -3613,7 +3626,7 @@
         <v>8.3699999999999992</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -3621,7 +3634,7 @@
         <v>8.84</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -3629,7 +3642,7 @@
         <v>11.49</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -3637,7 +3650,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -3645,7 +3658,7 @@
         <v>10.78</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -3653,7 +3666,7 @@
         <v>12.24</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -3661,7 +3674,7 @@
         <v>8.15</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -3669,7 +3682,7 @@
         <v>14.68</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -3677,7 +3690,7 @@
         <v>9.08</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -3685,7 +3698,7 @@
         <v>11.03</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -3693,7 +3706,7 @@
         <v>13.02</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -3701,7 +3714,7 @@
         <v>13.59</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -3709,7 +3722,7 @@
         <v>8.9700000000000006</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -3717,7 +3730,7 @@
         <v>11.03</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -3725,7 +3738,7 @@
         <v>11.91</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -3733,7 +3746,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -3741,7 +3754,7 @@
         <v>8.65</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -3749,7 +3762,7 @@
         <v>10.56</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -3757,7 +3770,7 @@
         <v>10.26</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -3765,7 +3778,7 @@
         <v>15.93</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -3773,7 +3786,7 @@
         <v>12.53</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>67</v>
       </c>
@@ -3781,7 +3794,7 @@
         <v>14.07</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>68</v>
       </c>
@@ -3804,15 +3817,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.140625" customWidth="1"/>
-    <col min="3" max="3" width="53.7109375" style="11" customWidth="1"/>
-    <col min="4" max="4" width="80.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.6640625" style="11" customWidth="1"/>
+    <col min="4" max="4" width="80.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>177</v>
       </c>
@@ -3826,7 +3839,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3840,7 +3853,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3854,7 +3867,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3868,7 +3881,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3882,7 +3895,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3896,7 +3909,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3911,7 +3924,7 @@
         <v>10.877536231884054</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3926,7 +3939,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3941,7 +3954,7 @@
         <v>2.9157453617373181</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3956,7 +3969,7 @@
         <v>3.5483997502243625E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3983,9 +3996,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C40"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>69</v>
       </c>
@@ -3996,7 +4009,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -4007,7 +4020,7 @@
         <v>134.69999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -4018,7 +4031,7 @@
         <v>174.1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -4029,7 +4042,7 @@
         <v>205.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -4040,7 +4053,7 @@
         <v>213.9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>76</v>
       </c>
@@ -4051,7 +4064,7 @@
         <v>290.3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>77</v>
       </c>
@@ -4062,7 +4075,7 @@
         <v>169.6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>78</v>
       </c>
@@ -4073,7 +4086,7 @@
         <v>123.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>79</v>
       </c>
@@ -4084,7 +4097,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>80</v>
       </c>
@@ -4095,7 +4108,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>81</v>
       </c>
@@ -4106,7 +4119,7 @@
         <v>312.5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>82</v>
       </c>
@@ -4117,7 +4130,7 @@
         <v>126.1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>83</v>
       </c>
@@ -4128,7 +4141,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>84</v>
       </c>
@@ -4139,7 +4152,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>85</v>
       </c>
@@ -4150,7 +4163,7 @@
         <v>233.6</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -4161,7 +4174,7 @@
         <v>231.2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -4172,7 +4185,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>88</v>
       </c>
@@ -4183,7 +4196,7 @@
         <v>176.4</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>89</v>
       </c>
@@ -4194,7 +4207,7 @@
         <v>153.9</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>90</v>
       </c>
@@ -4205,7 +4218,7 @@
         <v>205.6</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>91</v>
       </c>
@@ -4216,7 +4229,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>92</v>
       </c>
@@ -4227,7 +4240,7 @@
         <v>174.7</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>93</v>
       </c>
@@ -4238,7 +4251,7 @@
         <v>116.7</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>94</v>
       </c>
@@ -4249,7 +4262,7 @@
         <v>157.6</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>95</v>
       </c>
@@ -4260,7 +4273,7 @@
         <v>170.4</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>96</v>
       </c>
@@ -4271,7 +4284,7 @@
         <v>166.7</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>97</v>
       </c>
@@ -4282,7 +4295,7 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>98</v>
       </c>
@@ -4293,7 +4306,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>99</v>
       </c>
@@ -4304,7 +4317,7 @@
         <v>192.7</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>100</v>
       </c>
@@ -4315,7 +4328,7 @@
         <v>218.7</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>101</v>
       </c>
@@ -4326,7 +4339,7 @@
         <v>331.4</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>102</v>
       </c>
@@ -4337,7 +4350,7 @@
         <v>241.1</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>103</v>
       </c>
@@ -4348,7 +4361,7 @@
         <v>302.2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>104</v>
       </c>
@@ -4359,7 +4372,7 @@
         <v>164.2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>105</v>
       </c>
@@ -4370,7 +4383,7 @@
         <v>190.3</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>106</v>
       </c>
@@ -4381,7 +4394,7 @@
         <v>178.7</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>107</v>
       </c>
@@ -4392,7 +4405,7 @@
         <v>198.4</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>108</v>
       </c>
@@ -4403,7 +4416,7 @@
         <v>149.19999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>109</v>
       </c>
@@ -4414,7 +4427,7 @@
         <v>183.7</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>110</v>
       </c>
@@ -4440,13 +4453,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>177</v>
       </c>
@@ -4460,7 +4474,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4474,7 +4488,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4488,7 +4502,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4502,7 +4516,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4516,7 +4530,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4530,7 +4544,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4541,7 +4555,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4556,7 +4570,7 @@
         <v>-1.586363310899447</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4571,7 +4585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4585,7 +4599,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4612,12 +4626,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Q92"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>111</v>
       </c>
@@ -4634,7 +4648,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -4653,7 +4667,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>115</v>
       </c>
@@ -4672,7 +4686,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>116</v>
       </c>
@@ -4693,7 +4707,7 @@
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>117</v>
       </c>
@@ -4715,7 +4729,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>118</v>
       </c>
@@ -4734,7 +4748,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>119</v>
       </c>
@@ -4757,7 +4771,7 @@
       </c>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>120</v>
       </c>
@@ -4782,7 +4796,7 @@
         <v>0.59274421222389939</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>121</v>
       </c>
@@ -4807,7 +4821,7 @@
         <v>0.35134570112493102</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>122</v>
       </c>
@@ -4832,7 +4846,7 @@
         <v>0.32972389116242873</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>123</v>
       </c>
@@ -4857,7 +4871,7 @@
         <v>7.2320027859794092</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>124</v>
       </c>
@@ -4884,7 +4898,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>125</v>
       </c>
@@ -4903,7 +4917,7 @@
         <v>36.700000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>126</v>
       </c>
@@ -4925,7 +4939,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>127</v>
       </c>
@@ -4960,7 +4974,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>128</v>
       </c>
@@ -4997,7 +5011,7 @@
         <v>2.2929734174828799E-6</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>129</v>
       </c>
@@ -5030,7 +5044,7 @@
         <v>52.301864296413939</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>130</v>
       </c>
@@ -5061,7 +5075,7 @@
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>131</v>
       </c>
@@ -5080,7 +5094,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>132</v>
       </c>
@@ -5124,7 +5138,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>133</v>
       </c>
@@ -5170,7 +5184,7 @@
         <v>37.890315798928519</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>134</v>
       </c>
@@ -5216,7 +5230,7 @@
         <v>17.197101562845951</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>135</v>
       </c>
@@ -5262,7 +5276,7 @@
         <v>8.9732634098597135</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>136</v>
       </c>
@@ -5281,7 +5295,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>137</v>
       </c>
@@ -5300,7 +5314,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>138</v>
       </c>
@@ -5321,7 +5335,7 @@
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>139</v>
       </c>
@@ -5346,7 +5360,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>140</v>
       </c>
@@ -5365,7 +5379,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>141</v>
       </c>
@@ -5399,7 +5413,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>142</v>
       </c>
@@ -5433,7 +5447,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>143</v>
       </c>
@@ -5467,7 +5481,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>144</v>
       </c>
@@ -5501,7 +5515,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>145</v>
       </c>
@@ -5535,7 +5549,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>146</v>
       </c>
@@ -5569,7 +5583,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>147</v>
       </c>
@@ -5603,7 +5617,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>148</v>
       </c>
@@ -5637,7 +5651,7 @@
         <v>30.5</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>149</v>
       </c>
@@ -5671,7 +5685,7 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>150</v>
       </c>
@@ -5705,7 +5719,7 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>151</v>
       </c>
@@ -5739,7 +5753,7 @@
         <v>31.7</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>152</v>
       </c>
@@ -5773,7 +5787,7 @@
         <v>31.9</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>153</v>
       </c>
@@ -5807,7 +5821,7 @@
         <v>32.1</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>154</v>
       </c>
@@ -5841,7 +5855,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>155</v>
       </c>
@@ -5875,7 +5889,7 @@
         <v>32.799999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>156</v>
       </c>
@@ -5909,7 +5923,7 @@
         <v>33.299999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>157</v>
       </c>
@@ -5943,7 +5957,7 @@
         <v>33.299999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>158</v>
       </c>
@@ -5977,7 +5991,7 @@
         <v>33.4</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>159</v>
       </c>
@@ -6011,7 +6025,7 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>160</v>
       </c>
@@ -6045,7 +6059,7 @@
         <v>34.6</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>161</v>
       </c>
@@ -6079,7 +6093,7 @@
         <v>34.700000000000003</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>162</v>
       </c>
@@ -6113,7 +6127,7 @@
         <v>35.200000000000003</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>163</v>
       </c>
@@ -6147,7 +6161,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>164</v>
       </c>
@@ -6181,7 +6195,7 @@
         <v>36.700000000000003</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>165</v>
       </c>
@@ -6215,7 +6229,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>166</v>
       </c>
@@ -6249,7 +6263,7 @@
         <v>37.299999999999997</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>167</v>
       </c>
@@ -6283,7 +6297,7 @@
         <v>37.799999999999997</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>168</v>
       </c>
@@ -6317,7 +6331,7 @@
         <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>169</v>
       </c>
@@ -6351,7 +6365,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>170</v>
       </c>
@@ -6385,7 +6399,7 @@
         <v>38.799999999999997</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>171</v>
       </c>
@@ -6419,7 +6433,7 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>172</v>
       </c>
@@ -6453,7 +6467,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>173</v>
       </c>
@@ -6487,7 +6501,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>174</v>
       </c>
@@ -6521,7 +6535,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>175</v>
       </c>
@@ -6555,7 +6569,7 @@
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>176</v>
       </c>
@@ -6589,7 +6603,7 @@
         <v>40.9</v>
       </c>
     </row>
-    <row r="65" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I65">
         <v>36</v>
       </c>
@@ -6606,7 +6620,7 @@
         <v>41.1</v>
       </c>
     </row>
-    <row r="66" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I66">
         <v>37</v>
       </c>
@@ -6623,7 +6637,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="67" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I67">
         <v>38</v>
       </c>
@@ -6640,7 +6654,7 @@
         <v>41.8</v>
       </c>
     </row>
-    <row r="68" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I68">
         <v>39</v>
       </c>
@@ -6657,7 +6671,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="69" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I69">
         <v>40</v>
       </c>
@@ -6674,7 +6688,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="70" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I70">
         <v>41</v>
       </c>
@@ -6691,7 +6705,7 @@
         <v>43.8</v>
       </c>
     </row>
-    <row r="71" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I71">
         <v>42</v>
       </c>
@@ -6708,7 +6722,7 @@
         <v>44.3</v>
       </c>
     </row>
-    <row r="72" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I72">
         <v>43</v>
       </c>
@@ -6725,7 +6739,7 @@
         <v>44.5</v>
       </c>
     </row>
-    <row r="73" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I73">
         <v>44</v>
       </c>
@@ -6742,7 +6756,7 @@
         <v>44.7</v>
       </c>
     </row>
-    <row r="74" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I74">
         <v>45</v>
       </c>
@@ -6759,7 +6773,7 @@
         <v>44.8</v>
       </c>
     </row>
-    <row r="75" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I75">
         <v>46</v>
       </c>
@@ -6776,7 +6790,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="76" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I76">
         <v>47</v>
       </c>
@@ -6793,7 +6807,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="77" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I77">
         <v>48</v>
       </c>
@@ -6810,7 +6824,7 @@
         <v>46.4</v>
       </c>
     </row>
-    <row r="78" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I78">
         <v>49</v>
       </c>
@@ -6827,7 +6841,7 @@
         <v>46.4</v>
       </c>
     </row>
-    <row r="79" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I79">
         <v>50</v>
       </c>
@@ -6844,7 +6858,7 @@
         <v>46.5</v>
       </c>
     </row>
-    <row r="80" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I80">
         <v>51</v>
       </c>
@@ -6861,7 +6875,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="81" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I81">
         <v>52</v>
       </c>
@@ -6878,7 +6892,7 @@
         <v>47.1</v>
       </c>
     </row>
-    <row r="82" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I82">
         <v>53</v>
       </c>
@@ -6895,7 +6909,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="83" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I83">
         <v>54</v>
       </c>
@@ -6912,7 +6926,7 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="84" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I84">
         <v>55</v>
       </c>
@@ -6929,7 +6943,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="85" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I85">
         <v>56</v>
       </c>
@@ -6946,7 +6960,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="86" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I86">
         <v>57</v>
       </c>
@@ -6963,7 +6977,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="87" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I87">
         <v>58</v>
       </c>
@@ -6980,7 +6994,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="88" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I88">
         <v>59</v>
       </c>
@@ -6997,7 +7011,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="89" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I89">
         <v>60</v>
       </c>
@@ -7014,7 +7028,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="90" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I90">
         <v>61</v>
       </c>
@@ -7031,7 +7045,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="91" spans="9:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I91">
         <v>62</v>
       </c>
@@ -7048,7 +7062,7 @@
         <v>60.6</v>
       </c>
     </row>
-    <row r="92" spans="9:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="9:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I92" s="2">
         <v>63</v>
       </c>
@@ -7084,179 +7098,192 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="86" customWidth="1"/>
-    <col min="3" max="3" width="44.42578125" customWidth="1"/>
-    <col min="4" max="4" width="73.140625" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="56.5546875" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" customWidth="1"/>
+    <col min="4" max="4" width="73.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="13" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="13" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="13" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="13" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="13" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="13" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="13" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="13" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="13" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10">
+    <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A10" s="13">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="13">
         <v>12.712362560349812</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A11">
+    <row r="11" spans="1:4" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="D11">
+      <c r="C11" s="13"/>
+      <c r="D11" s="13">
         <v>0.32972389116242873</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12">
+    <row r="12" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="D12" t="str">
+      <c r="D12" s="13" t="str">
         <f>IF(Data3!N16&lt;0.05, "Reject Null Hypothesis", "Cannot Reject Null Hypothesis")</f>
         <v>Reject Null Hypothesis</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="14" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>
